--- a/DBs/nba/Results/NBA_2026_Results.xlsx
+++ b/DBs/nba/Results/NBA_2026_Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0072D-A047-424A-9650-8B2827A53164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105571EA-7AF1-4FA1-BC76-746E9970D5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12318" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13046" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -178,6 +178,18 @@
   <si>
     <t>CHH</t>
   </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
 </sst>
 </file>
 
@@ -236,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J2463" totalsRowShown="0">
-  <autoFilter ref="A1:J2463" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J2645" totalsRowShown="0">
+  <autoFilter ref="A1:J2645" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9606CA38-2371-480A-B2F8-3A23285B655E}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B29C85CC-3DBC-401B-A183-ABA3F92B96B9}" name="Season"/>
@@ -571,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB24B2-7646-4F57-8F9C-DF3DFCDB2AF4}">
-  <dimension ref="A1:J2463"/>
+  <dimension ref="A1:J2645"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -79401,6 +79413,5830 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2464" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2464" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2464">
+        <v>2026</v>
+      </c>
+      <c r="C2464" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2464">
+        <v>0.5</v>
+      </c>
+      <c r="E2464" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2464" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2464" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2464">
+        <v>126</v>
+      </c>
+      <c r="I2464">
+        <v>127</v>
+      </c>
+      <c r="J2464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2465" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2465">
+        <v>2026</v>
+      </c>
+      <c r="C2465" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2465">
+        <v>0.5</v>
+      </c>
+      <c r="E2465" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2465" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2465" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2465">
+        <v>127</v>
+      </c>
+      <c r="I2465">
+        <v>126</v>
+      </c>
+      <c r="J2465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2466" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2466">
+        <v>2026</v>
+      </c>
+      <c r="C2466" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2466">
+        <v>0.5</v>
+      </c>
+      <c r="E2466" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2466" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2466" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2466">
+        <v>114</v>
+      </c>
+      <c r="I2466">
+        <v>110</v>
+      </c>
+      <c r="J2466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2467" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2467">
+        <v>2026</v>
+      </c>
+      <c r="C2467" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2467">
+        <v>0.5</v>
+      </c>
+      <c r="E2467" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2467" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2467" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2467">
+        <v>110</v>
+      </c>
+      <c r="I2467">
+        <v>114</v>
+      </c>
+      <c r="J2467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2468" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B2468">
+        <v>2026</v>
+      </c>
+      <c r="C2468" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2468">
+        <v>0.5</v>
+      </c>
+      <c r="E2468" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2468" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2468" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2468">
+        <v>97</v>
+      </c>
+      <c r="I2468">
+        <v>109</v>
+      </c>
+      <c r="J2468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2469" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B2469">
+        <v>2026</v>
+      </c>
+      <c r="C2469" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2469">
+        <v>0.5</v>
+      </c>
+      <c r="E2469" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2469" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2469" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2469">
+        <v>109</v>
+      </c>
+      <c r="I2469">
+        <v>97</v>
+      </c>
+      <c r="J2469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2470" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B2470">
+        <v>2026</v>
+      </c>
+      <c r="C2470" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2470">
+        <v>0.5</v>
+      </c>
+      <c r="E2470" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2470" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2470" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2470">
+        <v>126</v>
+      </c>
+      <c r="I2470">
+        <v>121</v>
+      </c>
+      <c r="J2470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2471" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B2471">
+        <v>2026</v>
+      </c>
+      <c r="C2471" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2471">
+        <v>0.5</v>
+      </c>
+      <c r="E2471" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2471" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2471" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2471">
+        <v>121</v>
+      </c>
+      <c r="I2471">
+        <v>126</v>
+      </c>
+      <c r="J2471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2472" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B2472">
+        <v>2026</v>
+      </c>
+      <c r="C2472" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2472">
+        <v>0.5</v>
+      </c>
+      <c r="E2472" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2472" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2472" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2472">
+        <v>90</v>
+      </c>
+      <c r="I2472">
+        <v>121</v>
+      </c>
+      <c r="J2472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2473" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B2473">
+        <v>2026</v>
+      </c>
+      <c r="C2473" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2473">
+        <v>0.5</v>
+      </c>
+      <c r="E2473" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2473" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2473" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2473">
+        <v>121</v>
+      </c>
+      <c r="I2473">
+        <v>90</v>
+      </c>
+      <c r="J2473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2474" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B2474">
+        <v>2026</v>
+      </c>
+      <c r="C2474" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2474">
+        <v>0.5</v>
+      </c>
+      <c r="E2474" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2474" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2474" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2474">
+        <v>96</v>
+      </c>
+      <c r="I2474">
+        <v>111</v>
+      </c>
+      <c r="J2474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2475" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B2475">
+        <v>2026</v>
+      </c>
+      <c r="C2475" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2475">
+        <v>0.5</v>
+      </c>
+      <c r="E2475" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2475" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2475" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2475">
+        <v>111</v>
+      </c>
+      <c r="I2475">
+        <v>96</v>
+      </c>
+      <c r="J2475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2476" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2476">
+        <v>2026</v>
+      </c>
+      <c r="C2476" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2476">
+        <v>1</v>
+      </c>
+      <c r="E2476" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2476" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2476" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2476">
+        <v>113</v>
+      </c>
+      <c r="I2476">
+        <v>126</v>
+      </c>
+      <c r="J2476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2477" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2477">
+        <v>2026</v>
+      </c>
+      <c r="C2477" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2477">
+        <v>1</v>
+      </c>
+      <c r="E2477" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2477" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2477">
+        <v>126</v>
+      </c>
+      <c r="I2477">
+        <v>113</v>
+      </c>
+      <c r="J2477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2478" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2478">
+        <v>2026</v>
+      </c>
+      <c r="C2478" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2478">
+        <v>1</v>
+      </c>
+      <c r="E2478" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2478" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2478" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2478">
+        <v>105</v>
+      </c>
+      <c r="I2478">
+        <v>116</v>
+      </c>
+      <c r="J2478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2479" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2479">
+        <v>2026</v>
+      </c>
+      <c r="C2479" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2479">
+        <v>1</v>
+      </c>
+      <c r="E2479" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2479" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2479" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2479">
+        <v>116</v>
+      </c>
+      <c r="I2479">
+        <v>105</v>
+      </c>
+      <c r="J2479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2480" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2480">
+        <v>2026</v>
+      </c>
+      <c r="C2480" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2480">
+        <v>1</v>
+      </c>
+      <c r="E2480" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2480" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2480" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2480">
+        <v>102</v>
+      </c>
+      <c r="I2480">
+        <v>113</v>
+      </c>
+      <c r="J2480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2481" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2481">
+        <v>2026</v>
+      </c>
+      <c r="C2481" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2481">
+        <v>1</v>
+      </c>
+      <c r="E2481" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2481" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2481" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2481">
+        <v>113</v>
+      </c>
+      <c r="I2481">
+        <v>102</v>
+      </c>
+      <c r="J2481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2482" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2482">
+        <v>2026</v>
+      </c>
+      <c r="C2482" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2482">
+        <v>1</v>
+      </c>
+      <c r="E2482" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2482" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2482" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2482">
+        <v>98</v>
+      </c>
+      <c r="I2482">
+        <v>107</v>
+      </c>
+      <c r="J2482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2483" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B2483">
+        <v>2026</v>
+      </c>
+      <c r="C2483" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2483">
+        <v>1</v>
+      </c>
+      <c r="E2483" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2483" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2483" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2483">
+        <v>107</v>
+      </c>
+      <c r="I2483">
+        <v>98</v>
+      </c>
+      <c r="J2483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2484" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2484">
+        <v>2026</v>
+      </c>
+      <c r="C2484" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2484">
+        <v>1</v>
+      </c>
+      <c r="E2484" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2484" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2484" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2484">
+        <v>91</v>
+      </c>
+      <c r="I2484">
+        <v>123</v>
+      </c>
+      <c r="J2484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2485" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2485">
+        <v>2026</v>
+      </c>
+      <c r="C2485" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2485">
+        <v>1</v>
+      </c>
+      <c r="E2485" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2485" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2485" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2485">
+        <v>123</v>
+      </c>
+      <c r="I2485">
+        <v>91</v>
+      </c>
+      <c r="J2485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2486" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2486">
+        <v>2026</v>
+      </c>
+      <c r="C2486" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2486">
+        <v>1</v>
+      </c>
+      <c r="E2486" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2486" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2486" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2486">
+        <v>84</v>
+      </c>
+      <c r="I2486">
+        <v>119</v>
+      </c>
+      <c r="J2486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2487" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2487">
+        <v>2026</v>
+      </c>
+      <c r="C2487" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2487">
+        <v>1</v>
+      </c>
+      <c r="E2487" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2487" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2487">
+        <v>119</v>
+      </c>
+      <c r="I2487">
+        <v>84</v>
+      </c>
+      <c r="J2487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2488" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2488">
+        <v>2026</v>
+      </c>
+      <c r="C2488" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2488">
+        <v>1</v>
+      </c>
+      <c r="E2488" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2488" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2488">
+        <v>112</v>
+      </c>
+      <c r="I2488">
+        <v>101</v>
+      </c>
+      <c r="J2488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2489" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2489">
+        <v>2026</v>
+      </c>
+      <c r="C2489" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2489">
+        <v>1</v>
+      </c>
+      <c r="E2489" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2489" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2489">
+        <v>101</v>
+      </c>
+      <c r="I2489">
+        <v>112</v>
+      </c>
+      <c r="J2489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2490" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2490">
+        <v>2026</v>
+      </c>
+      <c r="C2490" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2490">
+        <v>1</v>
+      </c>
+      <c r="E2490" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2490" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2490">
+        <v>98</v>
+      </c>
+      <c r="I2490">
+        <v>111</v>
+      </c>
+      <c r="J2490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2491" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B2491">
+        <v>2026</v>
+      </c>
+      <c r="C2491" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2491">
+        <v>1</v>
+      </c>
+      <c r="E2491" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2491" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2491">
+        <v>111</v>
+      </c>
+      <c r="I2491">
+        <v>98</v>
+      </c>
+      <c r="J2491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2492" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2492">
+        <v>2026</v>
+      </c>
+      <c r="C2492" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2492">
+        <v>1</v>
+      </c>
+      <c r="E2492" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2492" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2492">
+        <v>105</v>
+      </c>
+      <c r="I2492">
+        <v>115</v>
+      </c>
+      <c r="J2492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2493" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2493">
+        <v>2026</v>
+      </c>
+      <c r="C2493" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2493">
+        <v>1</v>
+      </c>
+      <c r="E2493" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2493" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2493">
+        <v>115</v>
+      </c>
+      <c r="I2493">
+        <v>105</v>
+      </c>
+      <c r="J2493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2494" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2494">
+        <v>2026</v>
+      </c>
+      <c r="C2494" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2494">
+        <v>1</v>
+      </c>
+      <c r="E2494" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2494" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2494">
+        <v>107</v>
+      </c>
+      <c r="I2494">
+        <v>106</v>
+      </c>
+      <c r="J2494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2495" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2495">
+        <v>2026</v>
+      </c>
+      <c r="C2495" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2495">
+        <v>1</v>
+      </c>
+      <c r="E2495" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2495" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2495">
+        <v>106</v>
+      </c>
+      <c r="I2495">
+        <v>107</v>
+      </c>
+      <c r="J2495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2496" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2496">
+        <v>2026</v>
+      </c>
+      <c r="C2496" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2496">
+        <v>1</v>
+      </c>
+      <c r="E2496" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2496" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2496">
+        <v>119</v>
+      </c>
+      <c r="I2496">
+        <v>114</v>
+      </c>
+      <c r="J2496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2497" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2497">
+        <v>2026</v>
+      </c>
+      <c r="C2497" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2497">
+        <v>1</v>
+      </c>
+      <c r="E2497" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2497" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2497">
+        <v>114</v>
+      </c>
+      <c r="I2497">
+        <v>119</v>
+      </c>
+      <c r="J2497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2498" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2498">
+        <v>2026</v>
+      </c>
+      <c r="C2498" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2498">
+        <v>1</v>
+      </c>
+      <c r="E2498" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2498" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2498">
+        <v>111</v>
+      </c>
+      <c r="I2498">
+        <v>97</v>
+      </c>
+      <c r="J2498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2499" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2499">
+        <v>2026</v>
+      </c>
+      <c r="C2499" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2499">
+        <v>1</v>
+      </c>
+      <c r="E2499" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2499" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2499">
+        <v>97</v>
+      </c>
+      <c r="I2499">
+        <v>111</v>
+      </c>
+      <c r="J2499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2500" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2500">
+        <v>2026</v>
+      </c>
+      <c r="C2500" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2500">
+        <v>1</v>
+      </c>
+      <c r="E2500" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2500" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2500">
+        <v>106</v>
+      </c>
+      <c r="I2500">
+        <v>103</v>
+      </c>
+      <c r="J2500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2501" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2501">
+        <v>2026</v>
+      </c>
+      <c r="C2501" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2501">
+        <v>1</v>
+      </c>
+      <c r="E2501" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2501" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2501">
+        <v>103</v>
+      </c>
+      <c r="I2501">
+        <v>106</v>
+      </c>
+      <c r="J2501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2502" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2502">
+        <v>2026</v>
+      </c>
+      <c r="C2502" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2502">
+        <v>1</v>
+      </c>
+      <c r="E2502" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2502" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2502">
+        <v>94</v>
+      </c>
+      <c r="I2502">
+        <v>101</v>
+      </c>
+      <c r="J2502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2503" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2503">
+        <v>2026</v>
+      </c>
+      <c r="C2503" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2503">
+        <v>1</v>
+      </c>
+      <c r="E2503" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2503" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2503">
+        <v>101</v>
+      </c>
+      <c r="I2503">
+        <v>94</v>
+      </c>
+      <c r="J2503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2504" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B2504">
+        <v>2026</v>
+      </c>
+      <c r="C2504" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2504">
+        <v>1</v>
+      </c>
+      <c r="E2504" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2504" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2504">
+        <v>83</v>
+      </c>
+      <c r="I2504">
+        <v>98</v>
+      </c>
+      <c r="J2504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2505" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B2505">
+        <v>2026</v>
+      </c>
+      <c r="C2505" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2505">
+        <v>1</v>
+      </c>
+      <c r="E2505" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2505" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2505">
+        <v>98</v>
+      </c>
+      <c r="I2505">
+        <v>83</v>
+      </c>
+      <c r="J2505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2506" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B2506">
+        <v>2026</v>
+      </c>
+      <c r="C2506" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2506">
+        <v>1</v>
+      </c>
+      <c r="E2506" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2506" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2506">
+        <v>107</v>
+      </c>
+      <c r="I2506">
+        <v>120</v>
+      </c>
+      <c r="J2506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2507" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B2507">
+        <v>2026</v>
+      </c>
+      <c r="C2507" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2507">
+        <v>1</v>
+      </c>
+      <c r="E2507" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2507" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2507">
+        <v>120</v>
+      </c>
+      <c r="I2507">
+        <v>107</v>
+      </c>
+      <c r="J2507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2508" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2508">
+        <v>2026</v>
+      </c>
+      <c r="C2508" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2508">
+        <v>1</v>
+      </c>
+      <c r="E2508" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2508" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2508">
+        <v>108</v>
+      </c>
+      <c r="I2508">
+        <v>109</v>
+      </c>
+      <c r="J2508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2509" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2509">
+        <v>2026</v>
+      </c>
+      <c r="C2509" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2509">
+        <v>1</v>
+      </c>
+      <c r="E2509" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2509" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2509">
+        <v>109</v>
+      </c>
+      <c r="I2509">
+        <v>108</v>
+      </c>
+      <c r="J2509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2510" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2510">
+        <v>2026</v>
+      </c>
+      <c r="C2510" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2510">
+        <v>1</v>
+      </c>
+      <c r="E2510" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2510" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2510">
+        <v>104</v>
+      </c>
+      <c r="I2510">
+        <v>126</v>
+      </c>
+      <c r="J2510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2511" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2511">
+        <v>2026</v>
+      </c>
+      <c r="C2511" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2511">
+        <v>1</v>
+      </c>
+      <c r="E2511" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2511" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2511">
+        <v>126</v>
+      </c>
+      <c r="I2511">
+        <v>104</v>
+      </c>
+      <c r="J2511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2512" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2512">
+        <v>2026</v>
+      </c>
+      <c r="C2512" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2512">
+        <v>1</v>
+      </c>
+      <c r="E2512" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2512" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2512">
+        <v>96</v>
+      </c>
+      <c r="I2512">
+        <v>113</v>
+      </c>
+      <c r="J2512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2513" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2513">
+        <v>2026</v>
+      </c>
+      <c r="C2513" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2513">
+        <v>1</v>
+      </c>
+      <c r="E2513" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2513" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2513">
+        <v>113</v>
+      </c>
+      <c r="I2513">
+        <v>96</v>
+      </c>
+      <c r="J2513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2514" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2514">
+        <v>2026</v>
+      </c>
+      <c r="C2514" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2514">
+        <v>1</v>
+      </c>
+      <c r="E2514" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2514" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2514">
+        <v>108</v>
+      </c>
+      <c r="I2514">
+        <v>100</v>
+      </c>
+      <c r="J2514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2515" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2515">
+        <v>2026</v>
+      </c>
+      <c r="C2515" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2515">
+        <v>1</v>
+      </c>
+      <c r="E2515" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2515" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2515">
+        <v>100</v>
+      </c>
+      <c r="I2515">
+        <v>108</v>
+      </c>
+      <c r="J2515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2516" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2516">
+        <v>2026</v>
+      </c>
+      <c r="C2516" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2516">
+        <v>1</v>
+      </c>
+      <c r="E2516" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2516" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2516">
+        <v>112</v>
+      </c>
+      <c r="I2516">
+        <v>108</v>
+      </c>
+      <c r="J2516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2517" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2517">
+        <v>2026</v>
+      </c>
+      <c r="C2517" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2517">
+        <v>1</v>
+      </c>
+      <c r="E2517" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2517" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2517">
+        <v>108</v>
+      </c>
+      <c r="I2517">
+        <v>112</v>
+      </c>
+      <c r="J2517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2518" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2518">
+        <v>2026</v>
+      </c>
+      <c r="C2518" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2518">
+        <v>1</v>
+      </c>
+      <c r="E2518" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2518" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2518">
+        <v>120</v>
+      </c>
+      <c r="I2518">
+        <v>108</v>
+      </c>
+      <c r="J2518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2519" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2519">
+        <v>2026</v>
+      </c>
+      <c r="C2519" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2519">
+        <v>1</v>
+      </c>
+      <c r="E2519" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2519" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2519">
+        <v>108</v>
+      </c>
+      <c r="I2519">
+        <v>120</v>
+      </c>
+      <c r="J2519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2520" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2520">
+        <v>2026</v>
+      </c>
+      <c r="C2520" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2520">
+        <v>1</v>
+      </c>
+      <c r="E2520" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2520" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2520">
+        <v>105</v>
+      </c>
+      <c r="I2520">
+        <v>113</v>
+      </c>
+      <c r="J2520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2521" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2521">
+        <v>2026</v>
+      </c>
+      <c r="C2521" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2521">
+        <v>1</v>
+      </c>
+      <c r="E2521" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2521" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2521">
+        <v>113</v>
+      </c>
+      <c r="I2521">
+        <v>105</v>
+      </c>
+      <c r="J2521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2522" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2522">
+        <v>2026</v>
+      </c>
+      <c r="C2522" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2522">
+        <v>1</v>
+      </c>
+      <c r="E2522" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2522" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2522">
+        <v>121</v>
+      </c>
+      <c r="I2522">
+        <v>109</v>
+      </c>
+      <c r="J2522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2523" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2523">
+        <v>2026</v>
+      </c>
+      <c r="C2523" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2523">
+        <v>1</v>
+      </c>
+      <c r="E2523" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2523" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2523">
+        <v>109</v>
+      </c>
+      <c r="I2523">
+        <v>121</v>
+      </c>
+      <c r="J2523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2524" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2524">
+        <v>2026</v>
+      </c>
+      <c r="C2524" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2524">
+        <v>1</v>
+      </c>
+      <c r="E2524" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2524" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2524">
+        <v>114</v>
+      </c>
+      <c r="I2524">
+        <v>98</v>
+      </c>
+      <c r="J2524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2525" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2525">
+        <v>2026</v>
+      </c>
+      <c r="C2525" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2525">
+        <v>1</v>
+      </c>
+      <c r="E2525" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2525" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2525">
+        <v>98</v>
+      </c>
+      <c r="I2525">
+        <v>114</v>
+      </c>
+      <c r="J2525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2526" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2526">
+        <v>2026</v>
+      </c>
+      <c r="C2526" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2526">
+        <v>1</v>
+      </c>
+      <c r="E2526" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2526" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2526">
+        <v>96</v>
+      </c>
+      <c r="I2526">
+        <v>112</v>
+      </c>
+      <c r="J2526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2527" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B2527">
+        <v>2026</v>
+      </c>
+      <c r="C2527" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2527">
+        <v>1</v>
+      </c>
+      <c r="E2527" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2527" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2527">
+        <v>112</v>
+      </c>
+      <c r="I2527">
+        <v>96</v>
+      </c>
+      <c r="J2527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2528" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2528">
+        <v>2026</v>
+      </c>
+      <c r="C2528" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2528">
+        <v>1</v>
+      </c>
+      <c r="E2528" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2528" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2528">
+        <v>89</v>
+      </c>
+      <c r="I2528">
+        <v>93</v>
+      </c>
+      <c r="J2528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2529" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2529">
+        <v>2026</v>
+      </c>
+      <c r="C2529" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2529">
+        <v>1</v>
+      </c>
+      <c r="E2529" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2529" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2529">
+        <v>93</v>
+      </c>
+      <c r="I2529">
+        <v>89</v>
+      </c>
+      <c r="J2529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2530" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2530">
+        <v>2026</v>
+      </c>
+      <c r="C2530" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2530">
+        <v>1</v>
+      </c>
+      <c r="E2530" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2530" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2530">
+        <v>114</v>
+      </c>
+      <c r="I2530">
+        <v>93</v>
+      </c>
+      <c r="J2530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2531" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2531">
+        <v>2026</v>
+      </c>
+      <c r="C2531" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2531">
+        <v>1</v>
+      </c>
+      <c r="E2531" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2531" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2531">
+        <v>93</v>
+      </c>
+      <c r="I2531">
+        <v>114</v>
+      </c>
+      <c r="J2531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2532" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2532">
+        <v>2026</v>
+      </c>
+      <c r="C2532" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2532">
+        <v>1</v>
+      </c>
+      <c r="E2532" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2532" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2532">
+        <v>128</v>
+      </c>
+      <c r="I2532">
+        <v>96</v>
+      </c>
+      <c r="J2532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2533" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2533">
+        <v>2026</v>
+      </c>
+      <c r="C2533" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2533">
+        <v>1</v>
+      </c>
+      <c r="E2533" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2533" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2533">
+        <v>96</v>
+      </c>
+      <c r="I2533">
+        <v>128</v>
+      </c>
+      <c r="J2533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2534" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2534">
+        <v>2026</v>
+      </c>
+      <c r="C2534" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2534">
+        <v>1</v>
+      </c>
+      <c r="E2534" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2534" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2534">
+        <v>96</v>
+      </c>
+      <c r="I2534">
+        <v>115</v>
+      </c>
+      <c r="J2534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2535" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B2535">
+        <v>2026</v>
+      </c>
+      <c r="C2535" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2535">
+        <v>1</v>
+      </c>
+      <c r="E2535" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2535" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2535">
+        <v>115</v>
+      </c>
+      <c r="I2535">
+        <v>96</v>
+      </c>
+      <c r="J2535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2536" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2536">
+        <v>2026</v>
+      </c>
+      <c r="C2536" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2536">
+        <v>1</v>
+      </c>
+      <c r="E2536" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2536" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2536">
+        <v>88</v>
+      </c>
+      <c r="I2536">
+        <v>94</v>
+      </c>
+      <c r="J2536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2537" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2537">
+        <v>2026</v>
+      </c>
+      <c r="C2537" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2537">
+        <v>1</v>
+      </c>
+      <c r="E2537" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2537" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2537">
+        <v>94</v>
+      </c>
+      <c r="I2537">
+        <v>88</v>
+      </c>
+      <c r="J2537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2538" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2538">
+        <v>2026</v>
+      </c>
+      <c r="C2538" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2538">
+        <v>1</v>
+      </c>
+      <c r="E2538" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2538" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2538">
+        <v>131</v>
+      </c>
+      <c r="I2538">
+        <v>122</v>
+      </c>
+      <c r="J2538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2539" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2539">
+        <v>2026</v>
+      </c>
+      <c r="C2539" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2539">
+        <v>1</v>
+      </c>
+      <c r="E2539" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2539" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2539">
+        <v>122</v>
+      </c>
+      <c r="I2539">
+        <v>131</v>
+      </c>
+      <c r="J2539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2540" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2540">
+        <v>2026</v>
+      </c>
+      <c r="C2540" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2540">
+        <v>1</v>
+      </c>
+      <c r="E2540" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2540" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2540">
+        <v>113</v>
+      </c>
+      <c r="I2540">
+        <v>125</v>
+      </c>
+      <c r="J2540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2541" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2541">
+        <v>2026</v>
+      </c>
+      <c r="C2541" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2541">
+        <v>1</v>
+      </c>
+      <c r="E2541" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2541" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2541">
+        <v>125</v>
+      </c>
+      <c r="I2541">
+        <v>113</v>
+      </c>
+      <c r="J2541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2542" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2542">
+        <v>2026</v>
+      </c>
+      <c r="C2542" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2542">
+        <v>1</v>
+      </c>
+      <c r="E2542" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2542" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2542">
+        <v>113</v>
+      </c>
+      <c r="I2542">
+        <v>97</v>
+      </c>
+      <c r="J2542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2543" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2543">
+        <v>2026</v>
+      </c>
+      <c r="C2543" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2543">
+        <v>1</v>
+      </c>
+      <c r="E2543" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2543" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2543">
+        <v>97</v>
+      </c>
+      <c r="I2543">
+        <v>113</v>
+      </c>
+      <c r="J2543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2544" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2544">
+        <v>2026</v>
+      </c>
+      <c r="C2544" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2544">
+        <v>1</v>
+      </c>
+      <c r="E2544" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2544" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2544">
+        <v>97</v>
+      </c>
+      <c r="I2544">
+        <v>126</v>
+      </c>
+      <c r="J2544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2545" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2545">
+        <v>2026</v>
+      </c>
+      <c r="C2545" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2545">
+        <v>1</v>
+      </c>
+      <c r="E2545" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2545" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2545">
+        <v>126</v>
+      </c>
+      <c r="I2545">
+        <v>97</v>
+      </c>
+      <c r="J2545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2546" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2546">
+        <v>2026</v>
+      </c>
+      <c r="C2546" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2546">
+        <v>1</v>
+      </c>
+      <c r="E2546" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2546" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2546">
+        <v>95</v>
+      </c>
+      <c r="I2546">
+        <v>114</v>
+      </c>
+      <c r="J2546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2547" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2547">
+        <v>2026</v>
+      </c>
+      <c r="C2547" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2547">
+        <v>1</v>
+      </c>
+      <c r="E2547" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2547" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2547">
+        <v>114</v>
+      </c>
+      <c r="I2547">
+        <v>95</v>
+      </c>
+      <c r="J2547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2548" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2548">
+        <v>2026</v>
+      </c>
+      <c r="C2548" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2548">
+        <v>1</v>
+      </c>
+      <c r="E2548" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2548" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2548">
+        <v>109</v>
+      </c>
+      <c r="I2548">
+        <v>116</v>
+      </c>
+      <c r="J2548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2549" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2549">
+        <v>2026</v>
+      </c>
+      <c r="C2549" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2549">
+        <v>1</v>
+      </c>
+      <c r="E2549" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2549" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2549" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2549">
+        <v>116</v>
+      </c>
+      <c r="I2549">
+        <v>109</v>
+      </c>
+      <c r="J2549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2550" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2550">
+        <v>2026</v>
+      </c>
+      <c r="C2550" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2550">
+        <v>1</v>
+      </c>
+      <c r="E2550" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2550" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2550">
+        <v>120</v>
+      </c>
+      <c r="I2550">
+        <v>125</v>
+      </c>
+      <c r="J2550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2551" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2551">
+        <v>2026</v>
+      </c>
+      <c r="C2551" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2551">
+        <v>1</v>
+      </c>
+      <c r="E2551" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2551" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2551">
+        <v>125</v>
+      </c>
+      <c r="I2551">
+        <v>120</v>
+      </c>
+      <c r="J2551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2552" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2552">
+        <v>2026</v>
+      </c>
+      <c r="C2552" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2552">
+        <v>1</v>
+      </c>
+      <c r="E2552" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2552" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2552">
+        <v>99</v>
+      </c>
+      <c r="I2552">
+        <v>93</v>
+      </c>
+      <c r="J2552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2553" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2553">
+        <v>2026</v>
+      </c>
+      <c r="C2553" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2553">
+        <v>1</v>
+      </c>
+      <c r="E2553" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2553" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2553">
+        <v>93</v>
+      </c>
+      <c r="I2553">
+        <v>99</v>
+      </c>
+      <c r="J2553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2554" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2554">
+        <v>2026</v>
+      </c>
+      <c r="C2554" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2554">
+        <v>1</v>
+      </c>
+      <c r="E2554" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2554" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2554">
+        <v>140</v>
+      </c>
+      <c r="I2554">
+        <v>89</v>
+      </c>
+      <c r="J2554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2555" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2555">
+        <v>2026</v>
+      </c>
+      <c r="C2555" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2555">
+        <v>1</v>
+      </c>
+      <c r="E2555" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2555" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2555">
+        <v>89</v>
+      </c>
+      <c r="I2555">
+        <v>140</v>
+      </c>
+      <c r="J2555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2556" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2556">
+        <v>2026</v>
+      </c>
+      <c r="C2556" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2556">
+        <v>1</v>
+      </c>
+      <c r="E2556" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2556" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2556">
+        <v>93</v>
+      </c>
+      <c r="I2556">
+        <v>106</v>
+      </c>
+      <c r="J2556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2557" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2557">
+        <v>2026</v>
+      </c>
+      <c r="C2557" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2557">
+        <v>1</v>
+      </c>
+      <c r="E2557" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2557" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2557">
+        <v>106</v>
+      </c>
+      <c r="I2557">
+        <v>93</v>
+      </c>
+      <c r="J2557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2558" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2558">
+        <v>2026</v>
+      </c>
+      <c r="C2558" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2558">
+        <v>1</v>
+      </c>
+      <c r="E2558" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2558" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2558">
+        <v>98</v>
+      </c>
+      <c r="I2558">
+        <v>110</v>
+      </c>
+      <c r="J2558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2559" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2559">
+        <v>2026</v>
+      </c>
+      <c r="C2559" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2559">
+        <v>1</v>
+      </c>
+      <c r="E2559" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2559" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2559">
+        <v>110</v>
+      </c>
+      <c r="I2559">
+        <v>98</v>
+      </c>
+      <c r="J2559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2560" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2560">
+        <v>2026</v>
+      </c>
+      <c r="C2560" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2560">
+        <v>1</v>
+      </c>
+      <c r="E2560" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2560" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2560">
+        <v>93</v>
+      </c>
+      <c r="I2560">
+        <v>79</v>
+      </c>
+      <c r="J2560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2561" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2561">
+        <v>2026</v>
+      </c>
+      <c r="C2561" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2561">
+        <v>1</v>
+      </c>
+      <c r="E2561" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2561" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2561" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2561">
+        <v>79</v>
+      </c>
+      <c r="I2561">
+        <v>93</v>
+      </c>
+      <c r="J2561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2562" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2562">
+        <v>2026</v>
+      </c>
+      <c r="C2562" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2562">
+        <v>1</v>
+      </c>
+      <c r="E2562" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2562" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2562">
+        <v>110</v>
+      </c>
+      <c r="I2562">
+        <v>112</v>
+      </c>
+      <c r="J2562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2563" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2563">
+        <v>2026</v>
+      </c>
+      <c r="C2563" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2563">
+        <v>1</v>
+      </c>
+      <c r="E2563" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2563" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2563" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2563">
+        <v>112</v>
+      </c>
+      <c r="I2563">
+        <v>110</v>
+      </c>
+      <c r="J2563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2564" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2564">
+        <v>2026</v>
+      </c>
+      <c r="C2564" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2564">
+        <v>1</v>
+      </c>
+      <c r="E2564" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2564" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2564">
+        <v>98</v>
+      </c>
+      <c r="I2564">
+        <v>78</v>
+      </c>
+      <c r="J2564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2565" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B2565">
+        <v>2026</v>
+      </c>
+      <c r="C2565" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2565">
+        <v>1</v>
+      </c>
+      <c r="E2565" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2565" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2565">
+        <v>78</v>
+      </c>
+      <c r="I2565">
+        <v>98</v>
+      </c>
+      <c r="J2565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2566" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B2566">
+        <v>2026</v>
+      </c>
+      <c r="C2566" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2566">
+        <v>1</v>
+      </c>
+      <c r="E2566" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2566" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2566">
+        <v>109</v>
+      </c>
+      <c r="I2566">
+        <v>100</v>
+      </c>
+      <c r="J2566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2567" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B2567">
+        <v>2026</v>
+      </c>
+      <c r="C2567" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2567">
+        <v>1</v>
+      </c>
+      <c r="E2567" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2567" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2567">
+        <v>100</v>
+      </c>
+      <c r="I2567">
+        <v>109</v>
+      </c>
+      <c r="J2567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2568" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B2568">
+        <v>2026</v>
+      </c>
+      <c r="C2568" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2568">
+        <v>1</v>
+      </c>
+      <c r="E2568" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2568" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2568">
+        <v>94</v>
+      </c>
+      <c r="I2568">
+        <v>116</v>
+      </c>
+      <c r="J2568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2569" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B2569">
+        <v>2026</v>
+      </c>
+      <c r="C2569" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2569">
+        <v>1</v>
+      </c>
+      <c r="E2569" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2569" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2569">
+        <v>116</v>
+      </c>
+      <c r="I2569">
+        <v>94</v>
+      </c>
+      <c r="J2569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2570" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B2570">
+        <v>2026</v>
+      </c>
+      <c r="C2570" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2570">
+        <v>1</v>
+      </c>
+      <c r="E2570" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2570" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2570">
+        <v>102</v>
+      </c>
+      <c r="I2570">
+        <v>114</v>
+      </c>
+      <c r="J2570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2571" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B2571">
+        <v>2026</v>
+      </c>
+      <c r="C2571" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2571">
+        <v>1</v>
+      </c>
+      <c r="E2571" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2571" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2571" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2571">
+        <v>114</v>
+      </c>
+      <c r="I2571">
+        <v>102</v>
+      </c>
+      <c r="J2571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2572" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B2572">
+        <v>2026</v>
+      </c>
+      <c r="C2572" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2572">
+        <v>2</v>
+      </c>
+      <c r="E2572" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2572" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2572">
+        <v>98</v>
+      </c>
+      <c r="I2572">
+        <v>137</v>
+      </c>
+      <c r="J2572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2573" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B2573">
+        <v>2026</v>
+      </c>
+      <c r="C2573" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2573">
+        <v>2</v>
+      </c>
+      <c r="E2573" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2573" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2573" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2573">
+        <v>137</v>
+      </c>
+      <c r="I2573">
+        <v>98</v>
+      </c>
+      <c r="J2573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2574" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B2574">
+        <v>2026</v>
+      </c>
+      <c r="C2574" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2574">
+        <v>2</v>
+      </c>
+      <c r="E2574" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2574" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2574">
+        <v>104</v>
+      </c>
+      <c r="I2574">
+        <v>102</v>
+      </c>
+      <c r="J2574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2575" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B2575">
+        <v>2026</v>
+      </c>
+      <c r="C2575" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2575">
+        <v>2</v>
+      </c>
+      <c r="E2575" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2575" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2575">
+        <v>102</v>
+      </c>
+      <c r="I2575">
+        <v>104</v>
+      </c>
+      <c r="J2575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2576" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B2576">
+        <v>2026</v>
+      </c>
+      <c r="C2576" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2576">
+        <v>2</v>
+      </c>
+      <c r="E2576" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2576" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2576">
+        <v>101</v>
+      </c>
+      <c r="I2576">
+        <v>111</v>
+      </c>
+      <c r="J2576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2577" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B2577">
+        <v>2026</v>
+      </c>
+      <c r="C2577" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2577">
+        <v>2</v>
+      </c>
+      <c r="E2577" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2577" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2577">
+        <v>111</v>
+      </c>
+      <c r="I2577">
+        <v>101</v>
+      </c>
+      <c r="J2577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2578" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B2578">
+        <v>2026</v>
+      </c>
+      <c r="C2578" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2578">
+        <v>2</v>
+      </c>
+      <c r="E2578" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2578" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2578">
+        <v>90</v>
+      </c>
+      <c r="I2578">
+        <v>108</v>
+      </c>
+      <c r="J2578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2579" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B2579">
+        <v>2026</v>
+      </c>
+      <c r="C2579" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2579">
+        <v>2</v>
+      </c>
+      <c r="E2579" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2579" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2579" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2579">
+        <v>108</v>
+      </c>
+      <c r="I2579">
+        <v>90</v>
+      </c>
+      <c r="J2579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2580" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B2580">
+        <v>2026</v>
+      </c>
+      <c r="C2580" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2580">
+        <v>2</v>
+      </c>
+      <c r="E2580" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2580" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2580">
+        <v>102</v>
+      </c>
+      <c r="I2580">
+        <v>108</v>
+      </c>
+      <c r="J2580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2581" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B2581">
+        <v>2026</v>
+      </c>
+      <c r="C2581" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2581">
+        <v>2</v>
+      </c>
+      <c r="E2581" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2581" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2581">
+        <v>108</v>
+      </c>
+      <c r="I2581">
+        <v>102</v>
+      </c>
+      <c r="J2581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2582" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B2582">
+        <v>2026</v>
+      </c>
+      <c r="C2582" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2582">
+        <v>2</v>
+      </c>
+      <c r="E2582" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2582" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2582">
+        <v>95</v>
+      </c>
+      <c r="I2582">
+        <v>133</v>
+      </c>
+      <c r="J2582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2583" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B2583">
+        <v>2026</v>
+      </c>
+      <c r="C2583" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2583">
+        <v>2</v>
+      </c>
+      <c r="E2583" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2583" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2583">
+        <v>133</v>
+      </c>
+      <c r="I2583">
+        <v>95</v>
+      </c>
+      <c r="J2583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2584" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B2584">
+        <v>2026</v>
+      </c>
+      <c r="C2584" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2584">
+        <v>2</v>
+      </c>
+      <c r="E2584" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2584" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2584">
+        <v>97</v>
+      </c>
+      <c r="I2584">
+        <v>107</v>
+      </c>
+      <c r="J2584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2585" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B2585">
+        <v>2026</v>
+      </c>
+      <c r="C2585" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2585">
+        <v>2</v>
+      </c>
+      <c r="E2585" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2585" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2585">
+        <v>107</v>
+      </c>
+      <c r="I2585">
+        <v>97</v>
+      </c>
+      <c r="J2585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2586" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B2586">
+        <v>2026</v>
+      </c>
+      <c r="C2586" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2586">
+        <v>2</v>
+      </c>
+      <c r="E2586" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2586" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2586" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2586">
+        <v>107</v>
+      </c>
+      <c r="I2586">
+        <v>125</v>
+      </c>
+      <c r="J2586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2587" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B2587">
+        <v>2026</v>
+      </c>
+      <c r="C2587" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2587">
+        <v>2</v>
+      </c>
+      <c r="E2587" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2587" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2587" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2587">
+        <v>125</v>
+      </c>
+      <c r="I2587">
+        <v>107</v>
+      </c>
+      <c r="J2587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2588" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B2588">
+        <v>2026</v>
+      </c>
+      <c r="C2588" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2588">
+        <v>2</v>
+      </c>
+      <c r="E2588" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2588" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2588" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2588">
+        <v>108</v>
+      </c>
+      <c r="I2588">
+        <v>94</v>
+      </c>
+      <c r="J2588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2589" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B2589">
+        <v>2026</v>
+      </c>
+      <c r="C2589" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2589">
+        <v>2</v>
+      </c>
+      <c r="E2589" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2589" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2589">
+        <v>94</v>
+      </c>
+      <c r="I2589">
+        <v>108</v>
+      </c>
+      <c r="J2589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2590" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B2590">
+        <v>2026</v>
+      </c>
+      <c r="C2590" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2590">
+        <v>2</v>
+      </c>
+      <c r="E2590" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2590" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2590">
+        <v>115</v>
+      </c>
+      <c r="I2590">
+        <v>108</v>
+      </c>
+      <c r="J2590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2591" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B2591">
+        <v>2026</v>
+      </c>
+      <c r="C2591" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2591">
+        <v>2</v>
+      </c>
+      <c r="E2591" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2591" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2591">
+        <v>108</v>
+      </c>
+      <c r="I2591">
+        <v>115</v>
+      </c>
+      <c r="J2591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2592" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B2592">
+        <v>2026</v>
+      </c>
+      <c r="C2592" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2592">
+        <v>2</v>
+      </c>
+      <c r="E2592" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2592" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2592" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2592">
+        <v>109</v>
+      </c>
+      <c r="I2592">
+        <v>116</v>
+      </c>
+      <c r="J2592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2593" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B2593">
+        <v>2026</v>
+      </c>
+      <c r="C2593" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2593">
+        <v>2</v>
+      </c>
+      <c r="E2593" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2593" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2593">
+        <v>116</v>
+      </c>
+      <c r="I2593">
+        <v>109</v>
+      </c>
+      <c r="J2593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2594" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B2594">
+        <v>2026</v>
+      </c>
+      <c r="C2594" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2594">
+        <v>2</v>
+      </c>
+      <c r="E2594" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2594" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2594" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2594">
+        <v>131</v>
+      </c>
+      <c r="I2594">
+        <v>108</v>
+      </c>
+      <c r="J2594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2595" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B2595">
+        <v>2026</v>
+      </c>
+      <c r="C2595" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2595">
+        <v>2</v>
+      </c>
+      <c r="E2595" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2595" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2595">
+        <v>108</v>
+      </c>
+      <c r="I2595">
+        <v>131</v>
+      </c>
+      <c r="J2595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2596" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B2596">
+        <v>2026</v>
+      </c>
+      <c r="C2596" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2596">
+        <v>2</v>
+      </c>
+      <c r="E2596" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2596" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2596">
+        <v>144</v>
+      </c>
+      <c r="I2596">
+        <v>114</v>
+      </c>
+      <c r="J2596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2597" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B2597">
+        <v>2026</v>
+      </c>
+      <c r="C2597" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2597">
+        <v>2</v>
+      </c>
+      <c r="E2597" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2597" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2597" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2597">
+        <v>114</v>
+      </c>
+      <c r="I2597">
+        <v>144</v>
+      </c>
+      <c r="J2597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2598" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B2598">
+        <v>2026</v>
+      </c>
+      <c r="C2598" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2598">
+        <v>2</v>
+      </c>
+      <c r="E2598" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2598" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2598" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2598">
+        <v>109</v>
+      </c>
+      <c r="I2598">
+        <v>114</v>
+      </c>
+      <c r="J2598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2599" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B2599">
+        <v>2026</v>
+      </c>
+      <c r="C2599" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2599">
+        <v>2</v>
+      </c>
+      <c r="E2599" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2599" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2599" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2599">
+        <v>114</v>
+      </c>
+      <c r="I2599">
+        <v>109</v>
+      </c>
+      <c r="J2599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2600" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B2600">
+        <v>2026</v>
+      </c>
+      <c r="C2600" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2600">
+        <v>2</v>
+      </c>
+      <c r="E2600" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2600" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2600" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2600">
+        <v>103</v>
+      </c>
+      <c r="I2600">
+        <v>112</v>
+      </c>
+      <c r="J2600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2601" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B2601">
+        <v>2026</v>
+      </c>
+      <c r="C2601" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2601">
+        <v>2</v>
+      </c>
+      <c r="E2601" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2601" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2601" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2601">
+        <v>112</v>
+      </c>
+      <c r="I2601">
+        <v>103</v>
+      </c>
+      <c r="J2601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2602" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B2602">
+        <v>2026</v>
+      </c>
+      <c r="C2602" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2602">
+        <v>2</v>
+      </c>
+      <c r="E2602" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2602" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2602" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2602">
+        <v>115</v>
+      </c>
+      <c r="I2602">
+        <v>110</v>
+      </c>
+      <c r="J2602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2603" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B2603">
+        <v>2026</v>
+      </c>
+      <c r="C2603" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2603">
+        <v>2</v>
+      </c>
+      <c r="E2603" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2603" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2603" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2603">
+        <v>110</v>
+      </c>
+      <c r="I2603">
+        <v>115</v>
+      </c>
+      <c r="J2603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2604" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B2604">
+        <v>2026</v>
+      </c>
+      <c r="C2604" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2604">
+        <v>2</v>
+      </c>
+      <c r="E2604" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2604" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2604" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2604">
+        <v>97</v>
+      </c>
+      <c r="I2604">
+        <v>126</v>
+      </c>
+      <c r="J2604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2605" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B2605">
+        <v>2026</v>
+      </c>
+      <c r="C2605" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2605">
+        <v>2</v>
+      </c>
+      <c r="E2605" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2605" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2605" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2605">
+        <v>126</v>
+      </c>
+      <c r="I2605">
+        <v>97</v>
+      </c>
+      <c r="J2605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2606" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B2606">
+        <v>2026</v>
+      </c>
+      <c r="C2606" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2606">
+        <v>2</v>
+      </c>
+      <c r="E2606" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2606" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2606" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2606">
+        <v>117</v>
+      </c>
+      <c r="I2606">
+        <v>113</v>
+      </c>
+      <c r="J2606">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2607" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B2607">
+        <v>2026</v>
+      </c>
+      <c r="C2607" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2607">
+        <v>2</v>
+      </c>
+      <c r="E2607" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2607" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2607" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2607">
+        <v>113</v>
+      </c>
+      <c r="I2607">
+        <v>117</v>
+      </c>
+      <c r="J2607">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2608" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B2608">
+        <v>2026</v>
+      </c>
+      <c r="C2608" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2608">
+        <v>2</v>
+      </c>
+      <c r="E2608" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2608" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2608" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2608">
+        <v>115</v>
+      </c>
+      <c r="I2608">
+        <v>94</v>
+      </c>
+      <c r="J2608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2609" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B2609">
+        <v>2026</v>
+      </c>
+      <c r="C2609" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2609">
+        <v>2</v>
+      </c>
+      <c r="E2609" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2609" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2609" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2609">
+        <v>94</v>
+      </c>
+      <c r="I2609">
+        <v>115</v>
+      </c>
+      <c r="J2609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2610" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B2610">
+        <v>2026</v>
+      </c>
+      <c r="C2610" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2610">
+        <v>2</v>
+      </c>
+      <c r="E2610" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2610" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2610" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2610">
+        <v>139</v>
+      </c>
+      <c r="I2610">
+        <v>109</v>
+      </c>
+      <c r="J2610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2611" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B2611">
+        <v>2026</v>
+      </c>
+      <c r="C2611" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2611">
+        <v>2</v>
+      </c>
+      <c r="E2611" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2611" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2611" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2611">
+        <v>109</v>
+      </c>
+      <c r="I2611">
+        <v>139</v>
+      </c>
+      <c r="J2611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2612" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B2612">
+        <v>2026</v>
+      </c>
+      <c r="C2612" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2612">
+        <v>2</v>
+      </c>
+      <c r="E2612" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2612" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2612" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2612">
+        <v>125</v>
+      </c>
+      <c r="I2612">
+        <v>94</v>
+      </c>
+      <c r="J2612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2613" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B2613">
+        <v>2026</v>
+      </c>
+      <c r="C2613" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2613">
+        <v>2</v>
+      </c>
+      <c r="E2613" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2613" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2613" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2613">
+        <v>94</v>
+      </c>
+      <c r="I2613">
+        <v>125</v>
+      </c>
+      <c r="J2613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2614" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B2614">
+        <v>2026</v>
+      </c>
+      <c r="C2614" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2614">
+        <v>3</v>
+      </c>
+      <c r="E2614" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2614" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2614" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2614">
+        <v>122</v>
+      </c>
+      <c r="I2614">
+        <v>115</v>
+      </c>
+      <c r="J2614">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2615" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B2615">
+        <v>2026</v>
+      </c>
+      <c r="C2615" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2615">
+        <v>3</v>
+      </c>
+      <c r="E2615" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2615" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2615" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2615">
+        <v>115</v>
+      </c>
+      <c r="I2615">
+        <v>122</v>
+      </c>
+      <c r="J2615">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2616" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B2616">
+        <v>2026</v>
+      </c>
+      <c r="C2616" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2616">
+        <v>3</v>
+      </c>
+      <c r="E2616" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2616" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2616" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2616">
+        <v>104</v>
+      </c>
+      <c r="I2616">
+        <v>115</v>
+      </c>
+      <c r="J2616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2617" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B2617">
+        <v>2026</v>
+      </c>
+      <c r="C2617" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2617">
+        <v>3</v>
+      </c>
+      <c r="E2617" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2617" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2617">
+        <v>115</v>
+      </c>
+      <c r="I2617">
+        <v>104</v>
+      </c>
+      <c r="J2617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2618" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B2618">
+        <v>2026</v>
+      </c>
+      <c r="C2618" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2618">
+        <v>3</v>
+      </c>
+      <c r="E2618" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2618" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2618" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2618">
+        <v>113</v>
+      </c>
+      <c r="I2618">
+        <v>122</v>
+      </c>
+      <c r="J2618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2619" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B2619">
+        <v>2026</v>
+      </c>
+      <c r="C2619" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2619">
+        <v>3</v>
+      </c>
+      <c r="E2619" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2619" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2619" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2619">
+        <v>122</v>
+      </c>
+      <c r="I2619">
+        <v>113</v>
+      </c>
+      <c r="J2619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2620" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B2620">
+        <v>2026</v>
+      </c>
+      <c r="C2620" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2620">
+        <v>3</v>
+      </c>
+      <c r="E2620" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2620" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2620" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2620">
+        <v>93</v>
+      </c>
+      <c r="I2620">
+        <v>109</v>
+      </c>
+      <c r="J2620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2621" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B2621">
+        <v>2026</v>
+      </c>
+      <c r="C2621" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2621">
+        <v>3</v>
+      </c>
+      <c r="E2621" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2621" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2621" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2621">
+        <v>109</v>
+      </c>
+      <c r="I2621">
+        <v>93</v>
+      </c>
+      <c r="J2621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2622" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B2622">
+        <v>2026</v>
+      </c>
+      <c r="C2622" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2622">
+        <v>3</v>
+      </c>
+      <c r="E2622" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2622" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2622" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2622">
+        <v>123</v>
+      </c>
+      <c r="I2622">
+        <v>108</v>
+      </c>
+      <c r="J2622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2623" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B2623">
+        <v>2026</v>
+      </c>
+      <c r="C2623" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2623">
+        <v>3</v>
+      </c>
+      <c r="E2623" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2623" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2623" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2623">
+        <v>108</v>
+      </c>
+      <c r="I2623">
+        <v>123</v>
+      </c>
+      <c r="J2623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2624" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B2624">
+        <v>2026</v>
+      </c>
+      <c r="C2624" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2624">
+        <v>3</v>
+      </c>
+      <c r="E2624" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2624" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2624" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2624">
+        <v>121</v>
+      </c>
+      <c r="I2624">
+        <v>108</v>
+      </c>
+      <c r="J2624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2625" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B2625">
+        <v>2026</v>
+      </c>
+      <c r="C2625" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2625">
+        <v>3</v>
+      </c>
+      <c r="E2625" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2625" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2625" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2625">
+        <v>108</v>
+      </c>
+      <c r="I2625">
+        <v>121</v>
+      </c>
+      <c r="J2625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2626" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B2626">
+        <v>2026</v>
+      </c>
+      <c r="C2626" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2626">
+        <v>3</v>
+      </c>
+      <c r="E2626" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2626" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2626" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2626">
+        <v>82</v>
+      </c>
+      <c r="I2626">
+        <v>103</v>
+      </c>
+      <c r="J2626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2627" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B2627">
+        <v>2026</v>
+      </c>
+      <c r="C2627" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2627">
+        <v>3</v>
+      </c>
+      <c r="E2627" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2627" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2627" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2627">
+        <v>103</v>
+      </c>
+      <c r="I2627">
+        <v>82</v>
+      </c>
+      <c r="J2627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2628" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B2628">
+        <v>2026</v>
+      </c>
+      <c r="C2628" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2628">
+        <v>3</v>
+      </c>
+      <c r="E2628" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2628" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2628" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2628">
+        <v>130</v>
+      </c>
+      <c r="I2628">
+        <v>93</v>
+      </c>
+      <c r="J2628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2629" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B2629">
+        <v>2026</v>
+      </c>
+      <c r="C2629" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2629">
+        <v>3</v>
+      </c>
+      <c r="E2629" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2629" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2629" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2629">
+        <v>93</v>
+      </c>
+      <c r="I2629">
+        <v>130</v>
+      </c>
+      <c r="J2629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2630" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B2630">
+        <v>2026</v>
+      </c>
+      <c r="C2630" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2630">
+        <v>3</v>
+      </c>
+      <c r="E2630" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2630" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2630" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2630">
+        <v>114</v>
+      </c>
+      <c r="I2630">
+        <v>127</v>
+      </c>
+      <c r="J2630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2631" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B2631">
+        <v>2026</v>
+      </c>
+      <c r="C2631" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2631">
+        <v>3</v>
+      </c>
+      <c r="E2631" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2631" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2631" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2631">
+        <v>127</v>
+      </c>
+      <c r="I2631">
+        <v>114</v>
+      </c>
+      <c r="J2631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2632" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B2632">
+        <v>2026</v>
+      </c>
+      <c r="C2632" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2632">
+        <v>3</v>
+      </c>
+      <c r="E2632" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2632" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2632" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2632">
+        <v>91</v>
+      </c>
+      <c r="I2632">
+        <v>118</v>
+      </c>
+      <c r="J2632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2633" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B2633">
+        <v>2026</v>
+      </c>
+      <c r="C2633" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2633">
+        <v>3</v>
+      </c>
+      <c r="E2633" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2633" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2633" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2633">
+        <v>118</v>
+      </c>
+      <c r="I2633">
+        <v>91</v>
+      </c>
+      <c r="J2633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2634" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B2634">
+        <v>2026</v>
+      </c>
+      <c r="C2634" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2634">
+        <v>3</v>
+      </c>
+      <c r="E2634" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2634" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2634" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2634">
+        <v>111</v>
+      </c>
+      <c r="I2634">
+        <v>103</v>
+      </c>
+      <c r="J2634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2635" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B2635">
+        <v>2026</v>
+      </c>
+      <c r="C2635" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2635">
+        <v>3</v>
+      </c>
+      <c r="E2635" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2635" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2635" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2635">
+        <v>103</v>
+      </c>
+      <c r="I2635">
+        <v>111</v>
+      </c>
+      <c r="J2635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2636" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B2636">
+        <v>2026</v>
+      </c>
+      <c r="C2636" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2636">
+        <v>4</v>
+      </c>
+      <c r="E2636" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2636" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2636" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2636">
+        <v>105</v>
+      </c>
+      <c r="I2636">
+        <v>95</v>
+      </c>
+      <c r="J2636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2637" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B2637">
+        <v>2026</v>
+      </c>
+      <c r="C2637" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2637">
+        <v>4</v>
+      </c>
+      <c r="E2637" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2637" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2637" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2637">
+        <v>95</v>
+      </c>
+      <c r="I2637">
+        <v>105</v>
+      </c>
+      <c r="J2637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2638" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B2638">
+        <v>2026</v>
+      </c>
+      <c r="C2638" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2638">
+        <v>4</v>
+      </c>
+      <c r="E2638" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2638" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2638" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2638">
+        <v>105</v>
+      </c>
+      <c r="I2638">
+        <v>104</v>
+      </c>
+      <c r="J2638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2639" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B2639">
+        <v>2026</v>
+      </c>
+      <c r="C2639" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2639">
+        <v>4</v>
+      </c>
+      <c r="E2639" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2639" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2639" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2639">
+        <v>104</v>
+      </c>
+      <c r="I2639">
+        <v>105</v>
+      </c>
+      <c r="J2639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2640" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B2640">
+        <v>2026</v>
+      </c>
+      <c r="C2640" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2640">
+        <v>4</v>
+      </c>
+      <c r="E2640" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2640" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2640" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2640">
+        <v>115</v>
+      </c>
+      <c r="I2640">
+        <v>111</v>
+      </c>
+      <c r="J2640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2641" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B2641">
+        <v>2026</v>
+      </c>
+      <c r="C2641" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2641">
+        <v>4</v>
+      </c>
+      <c r="E2641" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2641" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2641" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2641">
+        <v>111</v>
+      </c>
+      <c r="I2641">
+        <v>115</v>
+      </c>
+      <c r="J2641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2642" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B2642">
+        <v>2026</v>
+      </c>
+      <c r="C2642" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2642">
+        <v>4</v>
+      </c>
+      <c r="E2642" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2642" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2642" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2642">
+        <v>106</v>
+      </c>
+      <c r="I2642">
+        <v>107</v>
+      </c>
+      <c r="J2642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2643" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B2643">
+        <v>2026</v>
+      </c>
+      <c r="C2643" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2643">
+        <v>4</v>
+      </c>
+      <c r="E2643" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2643" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2643" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2643">
+        <v>107</v>
+      </c>
+      <c r="I2643">
+        <v>106</v>
+      </c>
+      <c r="J2643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2644" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B2644">
+        <v>2026</v>
+      </c>
+      <c r="C2644" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2644">
+        <v>4</v>
+      </c>
+      <c r="E2644" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2644" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2644" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2644">
+        <v>94</v>
+      </c>
+      <c r="I2644">
+        <v>90</v>
+      </c>
+      <c r="J2644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2645" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B2645">
+        <v>2026</v>
+      </c>
+      <c r="C2645" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2645">
+        <v>4</v>
+      </c>
+      <c r="E2645" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2645" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2645" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2645">
+        <v>90</v>
+      </c>
+      <c r="I2645">
+        <v>94</v>
+      </c>
+      <c r="J2645">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/DBs/nba/Results/NBA_2026_Results.xlsx
+++ b/DBs/nba/Results/NBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105571EA-7AF1-4FA1-BC76-746E9970D5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68130CDF-95CA-4E1D-A86E-333F03BE7FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13046" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13046" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -177,18 +177,6 @@
   </si>
   <si>
     <t>CHH</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>SA</t>
   </si>
 </sst>
 </file>
@@ -79430,7 +79418,7 @@
         <v>39</v>
       </c>
       <c r="F2464" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2464" t="s">
         <v>12</v>
@@ -79459,7 +79447,7 @@
         <v>0.5</v>
       </c>
       <c r="E2465" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2465" t="s">
         <v>39</v>
@@ -79619,7 +79607,7 @@
         <v>0.5</v>
       </c>
       <c r="E2470" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F2470" t="s">
         <v>26</v>
@@ -79654,7 +79642,7 @@
         <v>26</v>
       </c>
       <c r="F2471" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G2471" t="s">
         <v>13</v>
@@ -79683,7 +79671,7 @@
         <v>0.5</v>
       </c>
       <c r="E2472" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2472" t="s">
         <v>29</v>
@@ -79718,7 +79706,7 @@
         <v>29</v>
       </c>
       <c r="F2473" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2473" t="s">
         <v>13</v>
@@ -79747,7 +79735,7 @@
         <v>0.5</v>
       </c>
       <c r="E2474" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F2474" t="s">
         <v>15</v>
@@ -79782,7 +79770,7 @@
         <v>15</v>
       </c>
       <c r="F2475" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G2475" t="s">
         <v>13</v>
@@ -79942,7 +79930,7 @@
         <v>21</v>
       </c>
       <c r="F2480" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2480" t="s">
         <v>12</v>
@@ -79971,7 +79959,7 @@
         <v>1</v>
       </c>
       <c r="E2481" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2481" t="s">
         <v>21</v>
@@ -80262,7 +80250,7 @@
         <v>33</v>
       </c>
       <c r="F2490" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2490" t="s">
         <v>12</v>
@@ -80291,7 +80279,7 @@
         <v>1</v>
       </c>
       <c r="E2491" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2491" t="s">
         <v>33</v>
@@ -80390,7 +80378,7 @@
         <v>21</v>
       </c>
       <c r="F2494" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2494" t="s">
         <v>12</v>
@@ -80419,7 +80407,7 @@
         <v>1</v>
       </c>
       <c r="E2495" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2495" t="s">
         <v>21</v>
@@ -80582,7 +80570,7 @@
         <v>33</v>
       </c>
       <c r="F2500" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2500" t="s">
         <v>12</v>
@@ -80611,7 +80599,7 @@
         <v>1</v>
       </c>
       <c r="E2501" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2501" t="s">
         <v>33</v>
@@ -80835,7 +80823,7 @@
         <v>1</v>
       </c>
       <c r="E2508" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2508" t="s">
         <v>21</v>
@@ -80870,7 +80858,7 @@
         <v>21</v>
       </c>
       <c r="F2509" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2509" t="s">
         <v>13</v>
@@ -81155,7 +81143,7 @@
         <v>1</v>
       </c>
       <c r="E2518" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2518" t="s">
         <v>33</v>
@@ -81190,7 +81178,7 @@
         <v>33</v>
       </c>
       <c r="F2519" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2519" t="s">
         <v>13</v>
@@ -81347,7 +81335,7 @@
         <v>1</v>
       </c>
       <c r="E2524" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2524" t="s">
         <v>21</v>
@@ -81382,7 +81370,7 @@
         <v>21</v>
       </c>
       <c r="F2525" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2525" t="s">
         <v>13</v>
@@ -81539,7 +81527,7 @@
         <v>1</v>
       </c>
       <c r="E2530" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2530" t="s">
         <v>33</v>
@@ -81574,7 +81562,7 @@
         <v>33</v>
       </c>
       <c r="F2531" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2531" t="s">
         <v>13</v>
@@ -81990,7 +81978,7 @@
         <v>21</v>
       </c>
       <c r="F2544" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2544" t="s">
         <v>12</v>
@@ -82019,7 +82007,7 @@
         <v>1</v>
       </c>
       <c r="E2545" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2545" t="s">
         <v>21</v>
@@ -82054,7 +82042,7 @@
         <v>33</v>
       </c>
       <c r="F2546" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2546" t="s">
         <v>12</v>
@@ -82083,7 +82071,7 @@
         <v>1</v>
       </c>
       <c r="E2547" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2547" t="s">
         <v>33</v>
@@ -82307,7 +82295,7 @@
         <v>1</v>
       </c>
       <c r="E2554" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2554" t="s">
         <v>21</v>
@@ -82342,7 +82330,7 @@
         <v>21</v>
       </c>
       <c r="F2555" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2555" t="s">
         <v>13</v>
@@ -82886,7 +82874,7 @@
         <v>31</v>
       </c>
       <c r="F2572" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2572" t="s">
         <v>12</v>
@@ -82915,7 +82903,7 @@
         <v>2</v>
       </c>
       <c r="E2573" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2573" t="s">
         <v>31</v>
@@ -82950,7 +82938,7 @@
         <v>34</v>
       </c>
       <c r="F2574" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2574" t="s">
         <v>12</v>
@@ -82979,7 +82967,7 @@
         <v>2</v>
       </c>
       <c r="E2575" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2575" t="s">
         <v>34</v>
@@ -83142,7 +83130,7 @@
         <v>31</v>
       </c>
       <c r="F2580" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2580" t="s">
         <v>12</v>
@@ -83171,7 +83159,7 @@
         <v>2</v>
       </c>
       <c r="E2581" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2581" t="s">
         <v>31</v>
@@ -83206,7 +83194,7 @@
         <v>34</v>
       </c>
       <c r="F2582" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2582" t="s">
         <v>12</v>
@@ -83235,7 +83223,7 @@
         <v>2</v>
       </c>
       <c r="E2583" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2583" t="s">
         <v>34</v>
@@ -83395,7 +83383,7 @@
         <v>2</v>
       </c>
       <c r="E2588" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2588" t="s">
         <v>31</v>
@@ -83430,7 +83418,7 @@
         <v>31</v>
       </c>
       <c r="F2589" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2589" t="s">
         <v>13</v>
@@ -83459,7 +83447,7 @@
         <v>2</v>
       </c>
       <c r="E2590" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2590" t="s">
         <v>34</v>
@@ -83494,7 +83482,7 @@
         <v>34</v>
       </c>
       <c r="F2591" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2591" t="s">
         <v>13</v>
@@ -83651,7 +83639,7 @@
         <v>2</v>
       </c>
       <c r="E2596" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2596" t="s">
         <v>31</v>
@@ -83686,7 +83674,7 @@
         <v>31</v>
       </c>
       <c r="F2597" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2597" t="s">
         <v>13</v>
@@ -83715,7 +83703,7 @@
         <v>2</v>
       </c>
       <c r="E2598" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2598" t="s">
         <v>34</v>
@@ -83750,7 +83738,7 @@
         <v>34</v>
       </c>
       <c r="F2599" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2599" t="s">
         <v>13</v>
@@ -83910,7 +83898,7 @@
         <v>34</v>
       </c>
       <c r="F2604" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2604" t="s">
         <v>12</v>
@@ -83939,7 +83927,7 @@
         <v>2</v>
       </c>
       <c r="E2605" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2605" t="s">
         <v>34</v>
@@ -84099,7 +84087,7 @@
         <v>2</v>
       </c>
       <c r="E2610" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2610" t="s">
         <v>34</v>
@@ -84134,7 +84122,7 @@
         <v>34</v>
       </c>
       <c r="F2611" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2611" t="s">
         <v>13</v>
@@ -84227,7 +84215,7 @@
         <v>3</v>
       </c>
       <c r="E2614" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2614" t="s">
         <v>38</v>
@@ -84262,7 +84250,7 @@
         <v>38</v>
       </c>
       <c r="F2615" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2615" t="s">
         <v>13</v>
@@ -84294,7 +84282,7 @@
         <v>14</v>
       </c>
       <c r="F2616" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2616" t="s">
         <v>12</v>
@@ -84323,7 +84311,7 @@
         <v>3</v>
       </c>
       <c r="E2617" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2617" t="s">
         <v>14</v>
@@ -84355,7 +84343,7 @@
         <v>3</v>
       </c>
       <c r="E2618" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2618" t="s">
         <v>38</v>
@@ -84390,7 +84378,7 @@
         <v>38</v>
       </c>
       <c r="F2619" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2619" t="s">
         <v>13</v>
@@ -84422,7 +84410,7 @@
         <v>14</v>
       </c>
       <c r="F2620" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2620" t="s">
         <v>12</v>
@@ -84451,7 +84439,7 @@
         <v>3</v>
       </c>
       <c r="E2621" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2621" t="s">
         <v>14</v>
@@ -84486,7 +84474,7 @@
         <v>38</v>
       </c>
       <c r="F2622" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2622" t="s">
         <v>12</v>
@@ -84515,7 +84503,7 @@
         <v>3</v>
       </c>
       <c r="E2623" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2623" t="s">
         <v>38</v>
@@ -84547,7 +84535,7 @@
         <v>3</v>
       </c>
       <c r="E2624" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2624" t="s">
         <v>14</v>
@@ -84582,7 +84570,7 @@
         <v>14</v>
       </c>
       <c r="F2625" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2625" t="s">
         <v>13</v>
@@ -84614,7 +84602,7 @@
         <v>38</v>
       </c>
       <c r="F2626" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2626" t="s">
         <v>12</v>
@@ -84643,7 +84631,7 @@
         <v>3</v>
       </c>
       <c r="E2627" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2627" t="s">
         <v>38</v>
@@ -84675,7 +84663,7 @@
         <v>3</v>
       </c>
       <c r="E2628" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2628" t="s">
         <v>14</v>
@@ -84710,7 +84698,7 @@
         <v>14</v>
       </c>
       <c r="F2629" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2629" t="s">
         <v>13</v>
@@ -84739,7 +84727,7 @@
         <v>3</v>
       </c>
       <c r="E2630" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2630" t="s">
         <v>38</v>
@@ -84774,7 +84762,7 @@
         <v>38</v>
       </c>
       <c r="F2631" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2631" t="s">
         <v>13</v>
@@ -84806,7 +84794,7 @@
         <v>38</v>
       </c>
       <c r="F2632" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2632" t="s">
         <v>12</v>
@@ -84835,7 +84823,7 @@
         <v>3</v>
       </c>
       <c r="E2633" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2633" t="s">
         <v>38</v>
@@ -84867,7 +84855,7 @@
         <v>3</v>
       </c>
       <c r="E2634" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2634" t="s">
         <v>38</v>
@@ -84902,7 +84890,7 @@
         <v>38</v>
       </c>
       <c r="F2635" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2635" t="s">
         <v>13</v>
@@ -84931,10 +84919,10 @@
         <v>4</v>
       </c>
       <c r="E2636" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2636" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2636" t="s">
         <v>12</v>
@@ -84963,10 +84951,10 @@
         <v>4</v>
       </c>
       <c r="E2637" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2637" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2637" t="s">
         <v>13</v>
@@ -84995,10 +84983,10 @@
         <v>4</v>
       </c>
       <c r="E2638" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2638" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2638" t="s">
         <v>12</v>
@@ -85027,10 +85015,10 @@
         <v>4</v>
       </c>
       <c r="E2639" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2639" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2639" t="s">
         <v>13</v>
@@ -85059,10 +85047,10 @@
         <v>4</v>
       </c>
       <c r="E2640" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2640" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2640" t="s">
         <v>12</v>
@@ -85091,10 +85079,10 @@
         <v>4</v>
       </c>
       <c r="E2641" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2641" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2641" t="s">
         <v>13</v>
@@ -85123,10 +85111,10 @@
         <v>4</v>
       </c>
       <c r="E2642" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2642" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2642" t="s">
         <v>12</v>
@@ -85155,10 +85143,10 @@
         <v>4</v>
       </c>
       <c r="E2643" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2643" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2643" t="s">
         <v>13</v>
@@ -85187,10 +85175,10 @@
         <v>4</v>
       </c>
       <c r="E2644" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2644" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G2644" t="s">
         <v>12</v>
@@ -85219,10 +85207,10 @@
         <v>4</v>
       </c>
       <c r="E2645" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F2645" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G2645" t="s">
         <v>13</v>
